--- a/(枠)◯年度一式/勤務形態表.xlsx
+++ b/(枠)◯年度一式/勤務形態表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="always" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\Desktop\R８年度一式\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137DDA04-F10E-4DA0-97EC-EA53EFB3DC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D78BCC-748F-4741-A3F2-5C03A9338E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="795" windowWidth="19395" windowHeight="15480" tabRatio="642" activeTab="8" xr2:uid="{C7B41DDB-AB3B-491E-920D-0FEC2791C8E4}"/>
+    <workbookView xWindow="5400" yWindow="375" windowWidth="20010" windowHeight="15480" tabRatio="642" activeTab="11" xr2:uid="{C7B41DDB-AB3B-491E-920D-0FEC2791C8E4}"/>
   </bookViews>
   <sheets>
     <sheet name="04" sheetId="1" r:id="rId1"/>
@@ -535,11 +535,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -574,16 +574,38 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Sheet1"/>
+      <sheetName val="A-1"/>
+      <sheetName val="A-2"/>
+      <sheetName val="B-1"/>
+      <sheetName val="収集（全般）"/>
+      <sheetName val="可燃"/>
+      <sheetName val="不燃・木くず・海岸清掃"/>
+      <sheetName val="ビン類"/>
+      <sheetName val="缶類"/>
+      <sheetName val="ペットボトル"/>
+      <sheetName val="紙類"/>
+      <sheetName val="粗大"/>
+      <sheetName val="産廃水産・医療・汚泥"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2">
-            <v>2026</v>
+        <row r="9">
+          <cell r="E9">
+            <v>2027</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -886,34 +908,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="19" t="str">
-        <f>[1]Sheet1!$B$2&amp;"令和年度　職員の勤務形態一覧表　　（予定）"</f>
-        <v>2026令和年度　職員の勤務形態一覧表　　（予定）</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20" t="s">
+      <c r="A1" s="20" t="str">
+        <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度　職員の勤務形態一覧表　　（予定）"</f>
+        <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="22" t="str">
-        <f>"（"&amp;[1]Sheet1!$B$2&amp;"年04月分）"</f>
-        <v>（2026年04月分）</v>
+        <f>"（"&amp;'[1]A-1'!$E$9&amp;"年04月分）"</f>
+        <v>（2027年04月分）</v>
       </c>
       <c r="B2" s="22"/>
       <c r="M2" s="7"/>
@@ -1415,15 +1437,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -1431,57 +1453,63 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19" t="s">
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19" t="s">
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19" t="s">
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19" t="s">
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O21:Q21"/>
@@ -1491,12 +1519,6 @@
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="1.5748031496062993" right="0" top="1.5748031496062993" bottom="0" header="0" footer="0"/>
@@ -1517,34 +1539,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="19" t="str">
+      <c r="A1" s="20" t="str">
         <f>'04'!A1:N1</f>
-        <v>2026令和年度　職員の勤務形態一覧表　　（予定）</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20" t="s">
+        <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A2" s="22" t="str">
-        <f>"（"&amp;[1]Sheet1!$B$2+1&amp;"年01月分）"</f>
-        <v>（2027年01月分）</v>
+        <f>"（"&amp;'[1]A-1'!$E$9+1&amp;"年01月分）"</f>
+        <v>（2028年01月分）</v>
       </c>
       <c r="B2" s="22"/>
       <c r="M2" s="7"/>
@@ -2047,15 +2069,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -2063,64 +2085,57 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19" t="s">
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19" t="s">
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19" t="s">
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19" t="s">
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="L24:N24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A2:B2"/>
@@ -2129,6 +2144,13 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="L24:N24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2148,34 +2170,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="19" t="str">
+      <c r="A1" s="20" t="str">
         <f>'04'!A1:N1</f>
-        <v>2026令和年度　職員の勤務形態一覧表　　（予定）</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20" t="s">
+        <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="22" t="str">
-        <f>"（"&amp;[1]Sheet1!$B$2+1&amp;"年02月分）"</f>
-        <v>（2027年02月分）</v>
+        <f>"（"&amp;'[1]A-1'!$E$9+1&amp;"年02月分）"</f>
+        <v>（2028年02月分）</v>
       </c>
       <c r="B2" s="22"/>
       <c r="M2" s="7"/>
@@ -2669,15 +2691,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -2685,64 +2707,57 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19" t="s">
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19" t="s">
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19" t="s">
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19" t="s">
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:Q25"/>
     <mergeCell ref="L22:N22"/>
@@ -2751,6 +2766,13 @@
     <mergeCell ref="O23:Q23"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2770,34 +2792,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="19" t="str">
+      <c r="A1" s="20" t="str">
         <f>'04'!A1:N1</f>
-        <v>2026令和年度　職員の勤務形態一覧表　　（予定）</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20" t="s">
+        <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="22" t="str">
-        <f>"（"&amp;[1]Sheet1!$B$2+1&amp;"年03月分）"</f>
-        <v>（2027年03月分）</v>
+        <f>"（"&amp;'[1]A-1'!$E$9+1&amp;"年03月分）"</f>
+        <v>（2028年03月分）</v>
       </c>
       <c r="B2" s="22"/>
       <c r="M2" s="7"/>
@@ -3303,15 +3325,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -3319,64 +3341,57 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19" t="s">
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19" t="s">
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19" t="s">
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19" t="s">
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="L24:N24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A2:B2"/>
@@ -3385,6 +3400,13 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="L24:N24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3404,34 +3426,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="19" t="str">
+      <c r="A1" s="20" t="str">
         <f>'04'!A1:N1</f>
-        <v>2026令和年度　職員の勤務形態一覧表　　（予定）</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20" t="s">
+        <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="22" t="str">
-        <f>"（"&amp;[1]Sheet1!$B$2&amp;"年05月分）"</f>
-        <v>（2026年05月分）</v>
+        <f>"（"&amp;'[1]A-1'!$E$9&amp;"年05月分）"</f>
+        <v>（2027年05月分）</v>
       </c>
       <c r="B2" s="22"/>
       <c r="M2" s="7"/>
@@ -3937,15 +3959,15 @@
       <c r="I21" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
       <c r="O21" s="21" t="s">
         <v>30</v>
       </c>
@@ -3953,64 +3975,57 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19" t="s">
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19" t="s">
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19" t="s">
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19" t="s">
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="L24:N24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A2:B2"/>
@@ -4019,6 +4034,13 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="L24:N24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4038,34 +4060,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="19" t="str">
+      <c r="A1" s="20" t="str">
         <f>'04'!A1:N1</f>
-        <v>2026令和年度　職員の勤務形態一覧表　　（予定）</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20" t="s">
+        <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="22" t="str">
-        <f>"（"&amp;[1]Sheet1!$B$2&amp;"年06月分）"</f>
-        <v>（2026年06月分）</v>
+        <f>"（"&amp;'[1]A-1'!$E$9&amp;"年06月分）"</f>
+        <v>（2027年06月分）</v>
       </c>
       <c r="B2" s="22"/>
       <c r="M2" s="7"/>
@@ -4567,15 +4589,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -4583,64 +4605,57 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19" t="s">
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19" t="s">
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19" t="s">
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19" t="s">
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:Q25"/>
     <mergeCell ref="L22:N22"/>
@@ -4649,6 +4664,13 @@
     <mergeCell ref="O23:Q23"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4668,34 +4690,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="19" t="str">
+      <c r="A1" s="20" t="str">
         <f>'04'!A1:N1</f>
-        <v>2026令和年度　職員の勤務形態一覧表　　（予定）</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20" t="s">
+        <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="22" t="str">
-        <f>"（"&amp;[1]Sheet1!$B$2&amp;"年07月分）"</f>
-        <v>（2026年07月分）</v>
+        <f>"（"&amp;'[1]A-1'!$E$9&amp;"年07月分）"</f>
+        <v>（2027年07月分）</v>
       </c>
       <c r="B2" s="22"/>
       <c r="M2" s="7"/>
@@ -5201,15 +5223,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -5217,64 +5239,57 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19" t="s">
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19" t="s">
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19" t="s">
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19" t="s">
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="L24:N24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A2:B2"/>
@@ -5283,6 +5298,13 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="L24:N24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5302,34 +5324,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="19" t="str">
+      <c r="A1" s="20" t="str">
         <f>'04'!A1:N1</f>
-        <v>2026令和年度　職員の勤務形態一覧表　　（予定）</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20" t="s">
+        <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="22" t="str">
-        <f>"（"&amp;[1]Sheet1!$B$2&amp;"年08月分）"</f>
-        <v>（2026年08月分）</v>
+        <f>"（"&amp;'[1]A-1'!$E$9&amp;"年08月分）"</f>
+        <v>（2027年08月分）</v>
       </c>
       <c r="B2" s="22"/>
       <c r="M2" s="7"/>
@@ -5835,15 +5857,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -5851,64 +5873,57 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19" t="s">
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19" t="s">
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19" t="s">
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19" t="s">
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:Q25"/>
     <mergeCell ref="L22:N22"/>
@@ -5917,6 +5932,13 @@
     <mergeCell ref="O23:Q23"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5936,34 +5958,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="19" t="str">
+      <c r="A1" s="20" t="str">
         <f>'04'!A1:N1</f>
-        <v>2026令和年度　職員の勤務形態一覧表　　（予定）</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20" t="s">
+        <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="22" t="str">
-        <f>"（"&amp;[1]Sheet1!$B$2&amp;"年09月分）"</f>
-        <v>（2026年09月分）</v>
+        <f>"（"&amp;'[1]A-1'!$E$9&amp;"年09月分）"</f>
+        <v>（2027年09月分）</v>
       </c>
       <c r="B2" s="22"/>
       <c r="M2" s="7"/>
@@ -6465,15 +6487,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -6481,64 +6503,57 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19" t="s">
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19" t="s">
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19" t="s">
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19" t="s">
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:Q25"/>
     <mergeCell ref="L22:N22"/>
@@ -6547,6 +6562,13 @@
     <mergeCell ref="O23:Q23"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6566,34 +6588,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="19" t="str">
+      <c r="A1" s="20" t="str">
         <f>'04'!A1:N1</f>
-        <v>2026令和年度　職員の勤務形態一覧表　　（予定）</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20" t="s">
+        <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="22" t="str">
-        <f>"（"&amp;[1]Sheet1!$B$2&amp;"年10月分）"</f>
-        <v>（2026年10月分）</v>
+        <f>"（"&amp;'[1]A-1'!$E$9&amp;"年10月分）"</f>
+        <v>（2027年10月分）</v>
       </c>
       <c r="B2" s="22"/>
       <c r="M2" s="7"/>
@@ -7099,15 +7121,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -7115,64 +7137,57 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19" t="s">
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19" t="s">
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19" t="s">
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19" t="s">
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:Q25"/>
     <mergeCell ref="L22:N22"/>
@@ -7181,6 +7196,13 @@
     <mergeCell ref="O23:Q23"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7200,34 +7222,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="19" t="str">
+      <c r="A1" s="20" t="str">
         <f>'04'!A1:N1</f>
-        <v>2026令和年度　職員の勤務形態一覧表　　（予定）</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20" t="s">
+        <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="22" t="str">
-        <f>"（"&amp;[1]Sheet1!$B$2&amp;"年11月分）"</f>
-        <v>（2026年11月分）</v>
+        <f>"（"&amp;'[1]A-1'!$E$9&amp;"年11月分）"</f>
+        <v>（2027年11月分）</v>
       </c>
       <c r="B2" s="22"/>
       <c r="M2" s="7"/>
@@ -7729,15 +7751,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -7745,64 +7767,57 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19" t="s">
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19" t="s">
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19" t="s">
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19" t="s">
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="L24:N24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A2:B2"/>
@@ -7811,6 +7826,13 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="L24:N24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7830,34 +7852,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="19" t="str">
+      <c r="A1" s="20" t="str">
         <f>'04'!A1:N1</f>
-        <v>2026令和年度　職員の勤務形態一覧表　　（予定）</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20" t="s">
+        <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="22" t="str">
-        <f>"（"&amp;[1]Sheet1!$B$2&amp;"年12月分）"</f>
-        <v>（2026年12月分）</v>
+        <f>"（"&amp;'[1]A-1'!$E$9&amp;"年12月分）"</f>
+        <v>（2027年12月分）</v>
       </c>
       <c r="B2" s="22"/>
       <c r="M2" s="7"/>
@@ -8363,15 +8385,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -8379,64 +8401,57 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19" t="s">
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19" t="s">
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19" t="s">
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19" t="s">
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="L24:N24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A2:B2"/>
@@ -8445,6 +8460,13 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="L24:N24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/(枠)◯年度一式/勤務形態表.xlsx
+++ b/(枠)◯年度一式/勤務形態表.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr updateLinks="always" defaultThemeVersion="124226"/>
+  <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D78BCC-748F-4741-A3F2-5C03A9338E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200CAA87-2C51-46E7-A077-60A2623224B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="375" windowWidth="20010" windowHeight="15480" tabRatio="642" activeTab="11" xr2:uid="{C7B41DDB-AB3B-491E-920D-0FEC2791C8E4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="642" xr2:uid="{C7B41DDB-AB3B-491E-920D-0FEC2791C8E4}"/>
   </bookViews>
   <sheets>
     <sheet name="04" sheetId="1" r:id="rId1"/>
@@ -535,11 +535,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -908,28 +908,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="19" t="str">
         <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度　職員の勤務形態一覧表　　（予定）"</f>
         <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="19" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
@@ -1437,15 +1437,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20" t="s">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -1453,63 +1453,57 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20" t="s">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20" t="s">
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20" t="s">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20" t="s">
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O21:Q21"/>
@@ -1519,6 +1513,12 @@
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="1.5748031496062993" right="0" top="1.5748031496062993" bottom="0" header="0" footer="0"/>
@@ -1539,28 +1539,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="19" t="str">
         <f>'04'!A1:N1</f>
         <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="19" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.15">
@@ -2069,15 +2069,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20" t="s">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -2085,57 +2085,64 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20" t="s">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20" t="s">
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20" t="s">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20" t="s">
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="L24:N24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A2:B2"/>
@@ -2144,13 +2151,6 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="L24:N24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2170,28 +2170,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="19" t="str">
         <f>'04'!A1:N1</f>
         <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="19" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
@@ -2691,15 +2691,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20" t="s">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -2707,57 +2707,64 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20" t="s">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20" t="s">
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20" t="s">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20" t="s">
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:Q25"/>
     <mergeCell ref="L22:N22"/>
@@ -2766,13 +2773,6 @@
     <mergeCell ref="O23:Q23"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2792,28 +2792,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="19" t="str">
         <f>'04'!A1:N1</f>
         <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="19" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
@@ -3325,15 +3325,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20" t="s">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -3341,57 +3341,64 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20" t="s">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20" t="s">
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20" t="s">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20" t="s">
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="L24:N24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A2:B2"/>
@@ -3400,13 +3407,6 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="L24:N24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3426,28 +3426,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="19" t="str">
         <f>'04'!A1:N1</f>
         <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="19" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
@@ -3959,15 +3959,15 @@
       <c r="I21" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20" t="s">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="21" t="s">
         <v>30</v>
       </c>
@@ -3975,57 +3975,64 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20" t="s">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20" t="s">
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20" t="s">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20" t="s">
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="L24:N24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A2:B2"/>
@@ -4034,13 +4041,6 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="L24:N24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4060,28 +4060,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="19" t="str">
         <f>'04'!A1:N1</f>
         <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="19" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
@@ -4589,15 +4589,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20" t="s">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -4605,57 +4605,64 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20" t="s">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20" t="s">
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20" t="s">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20" t="s">
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:Q25"/>
     <mergeCell ref="L22:N22"/>
@@ -4664,13 +4671,6 @@
     <mergeCell ref="O23:Q23"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4690,28 +4690,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="19" t="str">
         <f>'04'!A1:N1</f>
         <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="19" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
@@ -5223,15 +5223,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20" t="s">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -5239,57 +5239,64 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20" t="s">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20" t="s">
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20" t="s">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20" t="s">
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="L24:N24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A2:B2"/>
@@ -5298,13 +5305,6 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="L24:N24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5324,28 +5324,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="19" t="str">
         <f>'04'!A1:N1</f>
         <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="19" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
@@ -5857,15 +5857,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20" t="s">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -5873,57 +5873,64 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20" t="s">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20" t="s">
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20" t="s">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20" t="s">
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:Q25"/>
     <mergeCell ref="L22:N22"/>
@@ -5932,13 +5939,6 @@
     <mergeCell ref="O23:Q23"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5958,28 +5958,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="19" t="str">
         <f>'04'!A1:N1</f>
         <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="19" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
@@ -6487,15 +6487,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20" t="s">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -6503,57 +6503,64 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20" t="s">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20" t="s">
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20" t="s">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20" t="s">
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:Q25"/>
     <mergeCell ref="L22:N22"/>
@@ -6562,13 +6569,6 @@
     <mergeCell ref="O23:Q23"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6588,28 +6588,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="19" t="str">
         <f>'04'!A1:N1</f>
         <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="19" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
@@ -7121,15 +7121,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20" t="s">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -7137,57 +7137,64 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20" t="s">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20" t="s">
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20" t="s">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20" t="s">
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="P2:Q2"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:Q25"/>
     <mergeCell ref="L22:N22"/>
@@ -7196,13 +7203,6 @@
     <mergeCell ref="O23:Q23"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7222,28 +7222,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="19" t="str">
         <f>'04'!A1:N1</f>
         <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="19" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
@@ -7751,15 +7751,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20" t="s">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -7767,57 +7767,64 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20" t="s">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20" t="s">
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20" t="s">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20" t="s">
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="L24:N24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A2:B2"/>
@@ -7826,13 +7833,6 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="L24:N24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7852,28 +7852,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="19" t="str">
         <f>'04'!A1:N1</f>
         <v>令和9年度　職員の勤務形態一覧表　　（予定）</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="19" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
@@ -8385,15 +8385,15 @@
       <c r="I21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20" t="s">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="21" t="s">
         <v>14</v>
       </c>
@@ -8401,57 +8401,64 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20" t="s">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20" t="s">
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20" t="s">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20" t="s">
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="L24:N24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A2:B2"/>
@@ -8460,13 +8467,6 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="L24:N24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
